--- a/autohotkey 14.04.25.xlsx
+++ b/autohotkey 14.04.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="zz" sheetId="1" r:id="rId1"/>
@@ -10375,9 +10375,6 @@
     <t>ШКПЛ 5х2.5  -  … m</t>
   </si>
   <si>
-    <t>::zz43::Поръчка</t>
-  </si>
-  <si>
     <t>::qq15::python merge.py</t>
   </si>
   <si>
@@ -11366,6 +11363,9 @@
   </si>
   <si>
     <t>::qq25::python regex/main/text_source.py</t>
+  </si>
+  <si>
+    <t>::zz43::office@rait.bg</t>
   </si>
 </sst>
 </file>
@@ -13545,7 +13545,7 @@
         <v>34</v>
       </c>
       <c r="B233" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -13563,10 +13563,10 @@
     </row>
     <row r="236" spans="1:7">
       <c r="B236" t="s">
+        <v>3641</v>
+      </c>
+      <c r="G236" t="s">
         <v>3642</v>
-      </c>
-      <c r="G236" t="s">
-        <v>3643</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -13810,7 +13810,7 @@
         <v>43</v>
       </c>
       <c r="B280" t="s">
-        <v>3315</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -13875,16 +13875,16 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
+        <v>3622</v>
+      </c>
+      <c r="B292" t="s">
         <v>3623</v>
-      </c>
-      <c r="B292" t="s">
-        <v>3624</v>
       </c>
       <c r="F292" t="s">
         <v>47</v>
       </c>
       <c r="G292" s="7" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -18459,13 +18459,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="26" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="B34">
         <v>195125</v>
       </c>
       <c r="D34" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="0"/>
@@ -18474,13 +18474,13 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="26" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="B35">
         <v>195127</v>
       </c>
       <c r="D35" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="0"/>
@@ -18489,13 +18489,13 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="26" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="B36">
         <v>195128</v>
       </c>
       <c r="D36" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="0"/>
@@ -18504,13 +18504,13 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="26" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B37">
         <v>195129</v>
       </c>
       <c r="D37" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="0"/>
@@ -24508,13 +24508,13 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="B2" t="s">
+        <v>3432</v>
+      </c>
+      <c r="E2" t="s">
         <v>3433</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3434</v>
       </c>
       <c r="K2" t="str">
         <f>"::"&amp;A2&amp;"::"&amp;B2</f>
@@ -24523,13 +24523,13 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="B3" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E3" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K38" si="0">"::"&amp;A3&amp;"::"&amp;B3</f>
@@ -24538,13 +24538,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="B4" t="s">
+        <v>3435</v>
+      </c>
+      <c r="E4" t="s">
         <v>3436</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3437</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="0"/>
@@ -24553,13 +24553,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="B5" t="s">
+        <v>3437</v>
+      </c>
+      <c r="E5" t="s">
         <v>3438</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3439</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="0"/>
@@ -24568,13 +24568,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B6" t="s">
+        <v>3439</v>
+      </c>
+      <c r="E6" t="s">
         <v>3440</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3441</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="0"/>
@@ -24583,13 +24583,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B7" t="s">
+        <v>3441</v>
+      </c>
+      <c r="E7" t="s">
         <v>3442</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3443</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
@@ -24598,13 +24598,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B8" t="s">
+        <v>3443</v>
+      </c>
+      <c r="E8" t="s">
         <v>3444</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3445</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
@@ -24613,13 +24613,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B9" t="s">
+        <v>3445</v>
+      </c>
+      <c r="E9" t="s">
         <v>3446</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3447</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
@@ -24628,13 +24628,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B10" t="s">
+        <v>3447</v>
+      </c>
+      <c r="E10" t="s">
         <v>3448</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3449</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
@@ -24643,13 +24643,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B11" t="s">
+        <v>3449</v>
+      </c>
+      <c r="E11" t="s">
         <v>3450</v>
-      </c>
-      <c r="E11" t="s">
-        <v>3451</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
@@ -24658,13 +24658,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B12" t="s">
+        <v>3451</v>
+      </c>
+      <c r="E12" t="s">
         <v>3452</v>
-      </c>
-      <c r="E12" t="s">
-        <v>3453</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
@@ -24673,13 +24673,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B13" t="s">
+        <v>3453</v>
+      </c>
+      <c r="E13" t="s">
         <v>3454</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3455</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
@@ -24688,13 +24688,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B14" t="s">
+        <v>3455</v>
+      </c>
+      <c r="E14" t="s">
         <v>3456</v>
-      </c>
-      <c r="E14" t="s">
-        <v>3457</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
@@ -24703,13 +24703,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B15" t="s">
+        <v>3457</v>
+      </c>
+      <c r="E15" t="s">
         <v>3458</v>
-      </c>
-      <c r="E15" t="s">
-        <v>3459</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
@@ -24718,13 +24718,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="B16" t="s">
+        <v>3459</v>
+      </c>
+      <c r="E16" t="s">
         <v>3460</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3461</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
@@ -24733,13 +24733,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B17" t="s">
+        <v>3461</v>
+      </c>
+      <c r="E17" t="s">
         <v>3462</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3463</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
@@ -24748,13 +24748,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B18" t="s">
+        <v>3463</v>
+      </c>
+      <c r="E18" t="s">
         <v>3464</v>
-      </c>
-      <c r="E18" t="s">
-        <v>3465</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
@@ -24763,13 +24763,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B19" t="s">
+        <v>3465</v>
+      </c>
+      <c r="E19" t="s">
         <v>3466</v>
-      </c>
-      <c r="E19" t="s">
-        <v>3467</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="0"/>
@@ -24781,10 +24781,10 @@
         <v>1654</v>
       </c>
       <c r="B20" t="s">
+        <v>3467</v>
+      </c>
+      <c r="E20" t="s">
         <v>3468</v>
-      </c>
-      <c r="E20" t="s">
-        <v>3469</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="0"/>
@@ -24793,13 +24793,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B21" t="s">
+        <v>3469</v>
+      </c>
+      <c r="E21" t="s">
         <v>3470</v>
-      </c>
-      <c r="E21" t="s">
-        <v>3471</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="0"/>
@@ -24808,13 +24808,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="B22" t="s">
+        <v>3471</v>
+      </c>
+      <c r="E22" t="s">
         <v>3472</v>
-      </c>
-      <c r="E22" t="s">
-        <v>3473</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="0"/>
@@ -24823,13 +24823,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="B23" t="s">
+        <v>3473</v>
+      </c>
+      <c r="E23" t="s">
         <v>3474</v>
-      </c>
-      <c r="E23" t="s">
-        <v>3475</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="0"/>
@@ -24838,13 +24838,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="B24" t="s">
+        <v>3475</v>
+      </c>
+      <c r="E24" t="s">
         <v>3476</v>
-      </c>
-      <c r="E24" t="s">
-        <v>3477</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="0"/>
@@ -24853,13 +24853,13 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="B25" t="s">
+        <v>3477</v>
+      </c>
+      <c r="E25" t="s">
         <v>3478</v>
-      </c>
-      <c r="E25" t="s">
-        <v>3479</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="0"/>
@@ -24868,13 +24868,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="B26" t="s">
+        <v>3479</v>
+      </c>
+      <c r="E26" t="s">
         <v>3480</v>
-      </c>
-      <c r="E26" t="s">
-        <v>3481</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="0"/>
@@ -24883,13 +24883,13 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="B27" t="s">
+        <v>3481</v>
+      </c>
+      <c r="E27" t="s">
         <v>3482</v>
-      </c>
-      <c r="E27" t="s">
-        <v>3483</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="0"/>
@@ -24898,13 +24898,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="B28" t="s">
+        <v>3483</v>
+      </c>
+      <c r="E28" t="s">
         <v>3484</v>
-      </c>
-      <c r="E28" t="s">
-        <v>3485</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="0"/>
@@ -24913,13 +24913,13 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="B29" t="s">
+        <v>3485</v>
+      </c>
+      <c r="E29" t="s">
         <v>3486</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3487</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="0"/>
@@ -24928,13 +24928,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="B30" t="s">
+        <v>3487</v>
+      </c>
+      <c r="E30" t="s">
         <v>3488</v>
-      </c>
-      <c r="E30" t="s">
-        <v>3489</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="0"/>
@@ -24943,13 +24943,13 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="B31" t="s">
+        <v>3489</v>
+      </c>
+      <c r="E31" t="s">
         <v>3490</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3491</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="0"/>
@@ -24958,13 +24958,13 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="B32" t="s">
+        <v>3491</v>
+      </c>
+      <c r="E32" t="s">
         <v>3492</v>
-      </c>
-      <c r="E32" t="s">
-        <v>3493</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="0"/>
@@ -24973,13 +24973,13 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B33" t="s">
+        <v>3493</v>
+      </c>
+      <c r="E33" t="s">
         <v>3494</v>
-      </c>
-      <c r="E33" t="s">
-        <v>3495</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="0"/>
@@ -24988,13 +24988,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="B34" t="s">
+        <v>3495</v>
+      </c>
+      <c r="E34" t="s">
         <v>3496</v>
-      </c>
-      <c r="E34" t="s">
-        <v>3497</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="0"/>
@@ -25003,13 +25003,13 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="B35" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="E35" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="0"/>
@@ -25018,13 +25018,13 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="B36" t="s">
+        <v>3498</v>
+      </c>
+      <c r="E36" t="s">
         <v>3499</v>
-      </c>
-      <c r="E36" t="s">
-        <v>3500</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="0"/>
@@ -25033,13 +25033,13 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B37" t="s">
+        <v>3500</v>
+      </c>
+      <c r="E37" t="s">
         <v>3501</v>
-      </c>
-      <c r="E37" t="s">
-        <v>3502</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="0"/>
@@ -25048,13 +25048,13 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="B38" t="s">
+        <v>3502</v>
+      </c>
+      <c r="E38" t="s">
         <v>3503</v>
-      </c>
-      <c r="E38" t="s">
-        <v>3504</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="0"/>
@@ -26526,7 +26526,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -26541,22 +26541,22 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -27432,13 +27432,13 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="B2" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="D2" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="K2" t="str">
         <f>"::"&amp;A2&amp;"::"&amp;B2</f>
@@ -27447,13 +27447,13 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="B3" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="D3" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K20" si="0">"::"&amp;A3&amp;"::"&amp;B3</f>
@@ -27462,13 +27462,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="B4" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="D4" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="0"/>
@@ -27480,10 +27480,10 @@
         <v>1934</v>
       </c>
       <c r="B5" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="D5" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="0"/>
@@ -27495,10 +27495,10 @@
         <v>1935</v>
       </c>
       <c r="B6" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="D6" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="0"/>
@@ -27510,10 +27510,10 @@
         <v>1938</v>
       </c>
       <c r="B7" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="D7" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
@@ -27522,13 +27522,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="B8" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="D8" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
@@ -27537,13 +27537,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="B9" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="D9" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
@@ -27555,10 +27555,10 @@
         <v>1936</v>
       </c>
       <c r="B10" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="D10" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
@@ -27570,10 +27570,10 @@
         <v>1937</v>
       </c>
       <c r="B11" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="D11" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
@@ -27585,10 +27585,10 @@
         <v>1939</v>
       </c>
       <c r="B12" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="D12" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
@@ -27597,13 +27597,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="B13" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="D13" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
@@ -27612,13 +27612,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="B14" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="D14" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
@@ -27627,13 +27627,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="B15" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="D15" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
@@ -27642,13 +27642,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="B16" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="D16" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
@@ -27660,10 +27660,10 @@
         <v>1940</v>
       </c>
       <c r="B17" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="D17" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
@@ -27672,13 +27672,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="B18" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="D18" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
@@ -27687,13 +27687,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="B19" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D19" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="0"/>
@@ -27702,13 +27702,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="B20" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D20" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="0"/>
@@ -27727,18 +27727,18 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="B2" t="s">
+        <v>3367</v>
+      </c>
+      <c r="E2" t="s">
         <v>3368</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3369</v>
       </c>
       <c r="K2" t="str">
         <f>"::"&amp;A2&amp;"::"&amp;B2</f>
@@ -27747,13 +27747,13 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="B3" t="s">
+        <v>3369</v>
+      </c>
+      <c r="E3" t="s">
         <v>3370</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3371</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K12" si="0">"::"&amp;A3&amp;"::"&amp;B3</f>
@@ -27762,13 +27762,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="B4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="E4" t="s">
         <v>3372</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3373</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="0"/>
@@ -27777,13 +27777,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="B5" t="s">
+        <v>3373</v>
+      </c>
+      <c r="E5" t="s">
         <v>3374</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3375</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="0"/>
@@ -27792,13 +27792,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="B6" t="s">
+        <v>3375</v>
+      </c>
+      <c r="E6" t="s">
         <v>3376</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3377</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="0"/>
@@ -27807,13 +27807,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="B7" t="s">
+        <v>3377</v>
+      </c>
+      <c r="E7" t="s">
         <v>3378</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3379</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
@@ -27822,13 +27822,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="B8" t="s">
+        <v>3379</v>
+      </c>
+      <c r="E8" t="s">
         <v>3380</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3381</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
@@ -27837,13 +27837,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B9" t="s">
+        <v>3381</v>
+      </c>
+      <c r="E9" t="s">
         <v>3382</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3383</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
@@ -27852,13 +27852,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="B10" t="s">
+        <v>3383</v>
+      </c>
+      <c r="E10" t="s">
         <v>3384</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3385</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
@@ -27867,13 +27867,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="B11" t="s">
+        <v>3385</v>
+      </c>
+      <c r="E11" t="s">
         <v>3386</v>
-      </c>
-      <c r="E11" t="s">
-        <v>3387</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
@@ -27882,13 +27882,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="B12" t="s">
+        <v>3397</v>
+      </c>
+      <c r="E12" t="s">
         <v>3398</v>
-      </c>
-      <c r="E12" t="s">
-        <v>3399</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
@@ -27907,18 +27907,18 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="E2" t="s">
         <v>3509</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3510</v>
       </c>
       <c r="K2" t="str">
         <f>"::"&amp;A2&amp;"::"&amp;B2</f>
@@ -27927,13 +27927,13 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B3" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E3" t="s">
         <v>3511</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3512</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K33" si="0">"::"&amp;A3&amp;"::"&amp;B3</f>
@@ -27942,13 +27942,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B4" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E4" t="s">
         <v>3513</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3514</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="0"/>
@@ -27957,13 +27957,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B5" t="s">
+        <v>3514</v>
+      </c>
+      <c r="E5" t="s">
         <v>3515</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3516</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="0"/>
@@ -27972,13 +27972,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B6" t="s">
+        <v>3516</v>
+      </c>
+      <c r="E6" t="s">
         <v>3517</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3518</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="0"/>
@@ -27987,13 +27987,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="B7" t="s">
+        <v>3518</v>
+      </c>
+      <c r="E7" t="s">
         <v>3519</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3520</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
@@ -28002,13 +28002,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="B8" t="s">
+        <v>3520</v>
+      </c>
+      <c r="E8" t="s">
         <v>3521</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3522</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
@@ -28017,13 +28017,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="B9" t="s">
+        <v>3522</v>
+      </c>
+      <c r="E9" t="s">
         <v>3523</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3524</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
@@ -28032,13 +28032,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="B10" t="s">
+        <v>3524</v>
+      </c>
+      <c r="E10" t="s">
         <v>3525</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3526</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
@@ -28047,13 +28047,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="B11" t="s">
+        <v>3526</v>
+      </c>
+      <c r="E11" t="s">
         <v>3527</v>
-      </c>
-      <c r="E11" t="s">
-        <v>3528</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
@@ -28062,13 +28062,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="B12" t="s">
+        <v>3528</v>
+      </c>
+      <c r="E12" t="s">
         <v>3529</v>
-      </c>
-      <c r="E12" t="s">
-        <v>3530</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
@@ -28077,13 +28077,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="B13" t="s">
+        <v>3530</v>
+      </c>
+      <c r="E13" t="s">
         <v>3531</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3532</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
@@ -28092,13 +28092,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="B14" t="s">
+        <v>3532</v>
+      </c>
+      <c r="E14" t="s">
         <v>3533</v>
-      </c>
-      <c r="E14" t="s">
-        <v>3534</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
@@ -28107,13 +28107,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="B15" t="s">
+        <v>3534</v>
+      </c>
+      <c r="E15" t="s">
         <v>3535</v>
-      </c>
-      <c r="E15" t="s">
-        <v>3536</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
@@ -28122,13 +28122,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="B17" t="s">
+        <v>3550</v>
+      </c>
+      <c r="E17" t="s">
         <v>3551</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3552</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
@@ -28137,13 +28137,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="B18" t="s">
+        <v>3552</v>
+      </c>
+      <c r="E18" t="s">
         <v>3553</v>
-      </c>
-      <c r="E18" t="s">
-        <v>3554</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
@@ -28152,13 +28152,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="B19" t="s">
+        <v>3554</v>
+      </c>
+      <c r="E19" t="s">
         <v>3555</v>
-      </c>
-      <c r="E19" t="s">
-        <v>3556</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="0"/>
@@ -28167,13 +28167,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="B20" t="s">
+        <v>3556</v>
+      </c>
+      <c r="E20" t="s">
         <v>3557</v>
-      </c>
-      <c r="E20" t="s">
-        <v>3558</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="0"/>
@@ -28182,13 +28182,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="B21" t="s">
+        <v>3558</v>
+      </c>
+      <c r="E21" t="s">
         <v>3559</v>
-      </c>
-      <c r="E21" t="s">
-        <v>3560</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="0"/>
@@ -28197,13 +28197,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="B22" t="s">
+        <v>3560</v>
+      </c>
+      <c r="E22" t="s">
         <v>3561</v>
-      </c>
-      <c r="E22" t="s">
-        <v>3562</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="0"/>
@@ -28212,13 +28212,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="B23" t="s">
+        <v>3562</v>
+      </c>
+      <c r="E23" t="s">
         <v>3563</v>
-      </c>
-      <c r="E23" t="s">
-        <v>3564</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="0"/>
@@ -28227,13 +28227,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="B24" t="s">
+        <v>3564</v>
+      </c>
+      <c r="E24" t="s">
         <v>3565</v>
-      </c>
-      <c r="E24" t="s">
-        <v>3566</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="0"/>
@@ -28242,13 +28242,13 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="B25" t="s">
+        <v>3566</v>
+      </c>
+      <c r="E25" t="s">
         <v>3567</v>
-      </c>
-      <c r="E25" t="s">
-        <v>3568</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="0"/>
@@ -28257,13 +28257,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="B26" t="s">
+        <v>3568</v>
+      </c>
+      <c r="E26" t="s">
         <v>3569</v>
-      </c>
-      <c r="E26" t="s">
-        <v>3570</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="0"/>
@@ -28272,13 +28272,13 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="B27" t="s">
+        <v>3570</v>
+      </c>
+      <c r="E27" t="s">
         <v>3571</v>
-      </c>
-      <c r="E27" t="s">
-        <v>3572</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="0"/>
@@ -28287,13 +28287,13 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="B28" t="s">
+        <v>3572</v>
+      </c>
+      <c r="E28" t="s">
         <v>3573</v>
-      </c>
-      <c r="E28" t="s">
-        <v>3574</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="0"/>
@@ -28302,13 +28302,13 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="B29" t="s">
+        <v>3574</v>
+      </c>
+      <c r="E29" t="s">
         <v>3575</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3576</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="0"/>
@@ -28317,13 +28317,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="B30" t="s">
+        <v>3576</v>
+      </c>
+      <c r="E30" t="s">
         <v>3577</v>
-      </c>
-      <c r="E30" t="s">
-        <v>3578</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="0"/>
@@ -28332,13 +28332,13 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B31" t="s">
+        <v>3578</v>
+      </c>
+      <c r="E31" t="s">
         <v>3579</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3580</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="0"/>
@@ -28347,13 +28347,13 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="B32" t="s">
+        <v>3580</v>
+      </c>
+      <c r="E32" t="s">
         <v>3581</v>
-      </c>
-      <c r="E32" t="s">
-        <v>3582</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="0"/>
@@ -28362,13 +28362,13 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="B33" t="s">
+        <v>3582</v>
+      </c>
+      <c r="E33" t="s">
         <v>3583</v>
-      </c>
-      <c r="E33" t="s">
-        <v>3584</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="0"/>
@@ -37961,13 +37961,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
+        <v>3602</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3604</v>
+      </c>
+      <c r="E62" t="s">
         <v>3603</v>
-      </c>
-      <c r="B62" t="s">
-        <v>3605</v>
-      </c>
-      <c r="E62" t="s">
-        <v>3604</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -38505,10 +38505,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
+        <v>3605</v>
+      </c>
+      <c r="B164" t="s">
         <v>3606</v>
-      </c>
-      <c r="B164" t="s">
-        <v>3607</v>
       </c>
       <c r="E164">
         <v>92005001</v>
@@ -38521,10 +38521,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
+        <v>3607</v>
+      </c>
+      <c r="B167" t="s">
         <v>3608</v>
-      </c>
-      <c r="B167" t="s">
-        <v>3609</v>
       </c>
       <c r="E167">
         <v>92006501</v>
@@ -38601,13 +38601,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
+        <v>3611</v>
+      </c>
+      <c r="B183" t="s">
         <v>3612</v>
       </c>
-      <c r="B183" t="s">
+      <c r="E183" t="s">
         <v>3613</v>
-      </c>
-      <c r="E183" t="s">
-        <v>3614</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -38742,13 +38742,13 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
+        <v>3626</v>
+      </c>
+      <c r="B206" t="s">
         <v>3627</v>
       </c>
-      <c r="B206" t="s">
+      <c r="D206" t="s">
         <v>3628</v>
-      </c>
-      <c r="D206" t="s">
-        <v>3629</v>
       </c>
       <c r="H206" t="str">
         <f>"::"&amp;A206&amp;"::"&amp;B206</f>
@@ -38757,13 +38757,13 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="B207" t="s">
+        <v>3632</v>
+      </c>
+      <c r="D207" t="s">
         <v>3633</v>
-      </c>
-      <c r="D207" t="s">
-        <v>3634</v>
       </c>
       <c r="H207" t="str">
         <f>"::"&amp;A207&amp;"::"&amp;B207</f>
@@ -38772,13 +38772,13 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="B208" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="D208" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="H208" t="str">
         <f t="shared" ref="H208:H210" si="0">"::"&amp;A208&amp;"::"&amp;B208</f>
@@ -38787,13 +38787,13 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="B209" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="D209" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="H209" t="str">
         <f t="shared" si="0"/>
@@ -38802,13 +38802,13 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>3636</v>
+      </c>
+      <c r="B210" t="s">
         <v>3637</v>
       </c>
-      <c r="B210" t="s">
-        <v>3638</v>
-      </c>
       <c r="D210" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="H210" t="str">
         <f t="shared" si="0"/>

--- a/autohotkey 14.04.25.xlsx
+++ b/autohotkey 14.04.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="zz" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5589" uniqueCount="3646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5597" uniqueCount="3650">
   <si>
     <t>Здравей,</t>
   </si>
@@ -11366,6 +11366,18 @@
   </si>
   <si>
     <t>::zz43::office@rait.bg</t>
+  </si>
+  <si>
+    <t>xx6</t>
+  </si>
+  <si>
+    <t>xx8</t>
+  </si>
+  <si>
+    <t>::xx6::9280638</t>
+  </si>
+  <si>
+    <t>::xx8::9280834</t>
   </si>
 </sst>
 </file>
@@ -37507,7 +37519,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
@@ -37601,1216 +37613,1264 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B12" t="s">
-        <v>591</v>
+        <v>3646</v>
+      </c>
+      <c r="B12">
+        <v>9280638</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B13" t="s">
-        <v>592</v>
+        <v>3647</v>
+      </c>
+      <c r="B13">
+        <v>9280834</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="B14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="B15" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B16" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="B17" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="B18" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="B19" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>1913</v>
+        <v>1860</v>
       </c>
       <c r="B20" t="s">
-        <v>1905</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>1914</v>
+        <v>1861</v>
       </c>
       <c r="B21" t="s">
-        <v>1906</v>
+        <v>607</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="B22" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="B23" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>586</v>
+        <v>1915</v>
       </c>
       <c r="B24" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="B25" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>1921</v>
+        <v>586</v>
       </c>
       <c r="B26" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="B27" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>608</v>
+        <v>1921</v>
       </c>
       <c r="B28" t="s">
-        <v>610</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>598</v>
+        <v>1922</v>
       </c>
       <c r="B29" t="s">
-        <v>600</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>1647</v>
+        <v>608</v>
       </c>
       <c r="B30" t="s">
-        <v>1648</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>1650</v>
+        <v>598</v>
       </c>
       <c r="B31" t="s">
-        <v>1651</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>1834</v>
+        <v>1647</v>
       </c>
       <c r="B32" t="s">
-        <v>1836</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>1835</v>
+        <v>1650</v>
       </c>
       <c r="B33" t="s">
-        <v>1837</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>1896</v>
+        <v>1834</v>
       </c>
       <c r="B34" t="s">
-        <v>1897</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>1884</v>
+        <v>1835</v>
       </c>
       <c r="B35" t="s">
-        <v>1890</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>1885</v>
+        <v>1896</v>
       </c>
       <c r="B36" t="s">
-        <v>1891</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="B37" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="B38" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="B39" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B40" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>1840</v>
+        <v>1888</v>
       </c>
       <c r="B41" t="s">
-        <v>1841</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>1843</v>
+        <v>1889</v>
       </c>
       <c r="B42" t="s">
-        <v>1844</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>1850</v>
+        <v>1840</v>
       </c>
       <c r="B43" t="s">
-        <v>1851</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>1852</v>
+        <v>1843</v>
       </c>
       <c r="B44" t="s">
-        <v>1853</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
       <c r="B45" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>1847</v>
+        <v>1852</v>
       </c>
       <c r="B46" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>3053</v>
-      </c>
-      <c r="B47">
-        <v>617676</v>
+        <v>1846</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1848</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>3054</v>
-      </c>
-      <c r="B48">
-        <v>89117</v>
+        <v>1847</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B49">
+        <v>617676</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B50">
+        <v>89117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
         <v>595</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B52" t="s">
         <v>596</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E52" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="53" spans="1:5">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
         <v>1931</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B55" t="s">
         <v>1932</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E55" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="56" spans="1:5">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
         <v>601</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B58" t="s">
         <v>602</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E58" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="B57" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="59" spans="1:5">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
         <v>1919</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B61" t="s">
         <v>1918</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E61" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="62" spans="1:5">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
         <v>3602</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B64" t="s">
         <v>3604</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E64" t="s">
         <v>3603</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="65" spans="1:5">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
         <v>1917</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B67" t="s">
         <v>2226</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E67" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="B66" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="68" spans="1:5">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
         <v>588</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B70" t="s">
         <v>1879</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E70" t="s">
         <v>1874</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
-      <c r="B69" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="71" spans="1:5">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
         <v>589</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
         <v>1880</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E73" t="s">
         <v>1875</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="B72" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="74" spans="1:5">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
         <v>590</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B76" t="s">
         <v>1881</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E76" t="s">
         <v>1876</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
-      <c r="B75" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="77" spans="1:5">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
         <v>582</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B79" t="s">
         <v>1882</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E79" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="80" spans="1:5">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
         <v>603</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B82" t="s">
         <v>1883</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E82" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
-      <c r="B81" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="83" spans="1:5">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>3646</v>
+      </c>
+      <c r="B85" t="s">
+        <v>3648</v>
+      </c>
+      <c r="E85">
+        <v>9280638</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>3647</v>
+      </c>
+      <c r="B88" t="s">
+        <v>3649</v>
+      </c>
+      <c r="E88">
+        <v>9280834</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
         <v>1862</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B91" t="s">
         <v>1866</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E91" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
+    <row r="92" spans="1:5">
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
         <v>1863</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B94" t="s">
         <v>1867</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E94" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="B87" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" t="s">
+    <row r="95" spans="1:5">
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
         <v>1864</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B97" t="s">
         <v>1868</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E97" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
-      <c r="B90" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
+    <row r="98" spans="1:5">
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
         <v>1865</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B100" t="s">
         <v>1869</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E100" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="B93" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" t="s">
+    <row r="101" spans="1:5">
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
         <v>1858</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B103" t="s">
         <v>1870</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E103" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" t="s">
+    <row r="104" spans="1:5">
+      <c r="B104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
         <v>1859</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B106" t="s">
         <v>1873</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E106" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="B99" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" t="s">
+    <row r="107" spans="1:5">
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
         <v>1860</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B109" t="s">
         <v>1871</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E109" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
-      <c r="B102" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" t="s">
+    <row r="110" spans="1:5">
+      <c r="B110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
         <v>1861</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B112" t="s">
         <v>1872</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E112" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
-      <c r="B105" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" t="s">
+    <row r="113" spans="1:5">
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
         <v>1913</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B115" t="s">
         <v>1930</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E115" t="s">
         <v>1905</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="B108" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" t="s">
+    <row r="116" spans="1:5">
+      <c r="B116" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
         <v>1914</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B118" t="s">
         <v>1929</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E118" t="s">
         <v>1906</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
-      <c r="B111" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" t="s">
+    <row r="119" spans="1:5">
+      <c r="B119" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
         <v>1915</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B121" t="s">
         <v>1928</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E121" t="s">
         <v>1907</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
-      <c r="B114" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" t="s">
+    <row r="122" spans="1:5">
+      <c r="B122" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
         <v>1916</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B124" t="s">
         <v>1927</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E124" t="s">
         <v>1908</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
-      <c r="B117" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" t="s">
+    <row r="125" spans="1:5">
+      <c r="B125" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
         <v>586</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B127" t="s">
         <v>1926</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E127" t="s">
         <v>1909</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
-      <c r="B120" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" t="s">
+    <row r="128" spans="1:5">
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
         <v>1920</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B130" t="s">
         <v>1925</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E130" t="s">
         <v>1910</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
-      <c r="B123" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" t="s">
+    <row r="131" spans="1:5">
+      <c r="B131" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
         <v>1921</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B133" t="s">
         <v>1924</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E133" t="s">
         <v>1911</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
-      <c r="B126" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" t="s">
+    <row r="134" spans="1:5">
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
         <v>1922</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B136" t="s">
         <v>1923</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E136" t="s">
         <v>1912</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
-      <c r="B129" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" t="s">
+    <row r="137" spans="1:5">
+      <c r="B137" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
         <v>608</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B139" t="s">
         <v>609</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E139" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
-      <c r="B132" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" t="s">
+    <row r="140" spans="1:5">
+      <c r="B140" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
         <v>598</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B142" t="s">
         <v>599</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E142" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
-      <c r="B135" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" t="s">
+    <row r="143" spans="1:5">
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
         <v>1647</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B145" t="s">
         <v>1649</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E145" t="s">
         <v>1648</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
-      <c r="B138" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" t="s">
+    <row r="146" spans="1:5">
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
         <v>1650</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B148" t="s">
         <v>1652</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E148" t="s">
         <v>1651</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
-      <c r="B141" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" t="s">
+    <row r="149" spans="1:5">
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
         <v>1834</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B151" t="s">
         <v>1838</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E151" t="s">
         <v>1836</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
-      <c r="B144" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" t="s">
+    <row r="152" spans="1:5">
+      <c r="B152" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
         <v>1835</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B154" t="s">
         <v>1839</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E154" t="s">
         <v>1837</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
-      <c r="B147" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" t="s">
+    <row r="155" spans="1:5">
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
         <v>1896</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B157" t="s">
         <v>1898</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E157" t="s">
         <v>1897</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
-      <c r="B150" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" t="s">
+    <row r="158" spans="1:5">
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
         <v>1884</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B160" t="s">
         <v>1899</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E160" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
-      <c r="B153" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" t="s">
+    <row r="161" spans="1:5">
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
         <v>1885</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B163" t="s">
         <v>1900</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E163" t="s">
         <v>1891</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
-      <c r="B156" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" t="s">
+    <row r="164" spans="1:5">
+      <c r="B164" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
         <v>1886</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B166" t="s">
         <v>1901</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E166" t="s">
         <v>1892</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
-      <c r="B159" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" t="s">
+    <row r="167" spans="1:5">
+      <c r="B167" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
         <v>1887</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B169" t="s">
         <v>1902</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E169" t="s">
         <v>1893</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
-      <c r="B162" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
-      <c r="A164" t="s">
+    <row r="170" spans="1:5">
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
         <v>3605</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B172" t="s">
         <v>3606</v>
       </c>
-      <c r="E164">
+      <c r="E172">
         <v>92005001</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
-      <c r="B165" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
-      <c r="A167" t="s">
+    <row r="173" spans="1:5">
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
         <v>3607</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B175" t="s">
         <v>3608</v>
       </c>
-      <c r="E167">
+      <c r="E175">
         <v>92006501</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
-      <c r="B168" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
-      <c r="A170" t="s">
+    <row r="176" spans="1:5">
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
         <v>1888</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B178" t="s">
         <v>1903</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E178" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
-      <c r="B171" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" t="s">
+    <row r="179" spans="1:5">
+      <c r="B179" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
         <v>1889</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B181" t="s">
         <v>1904</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E181" t="s">
         <v>1895</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
-      <c r="B174" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" t="s">
+    <row r="182" spans="1:5">
+      <c r="B182" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
         <v>1840</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B185" t="s">
         <v>1842</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E185" t="s">
         <v>1841</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
-      <c r="B178" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" t="s">
+    <row r="186" spans="1:5">
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
         <v>1843</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B188" t="s">
         <v>1845</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E188" t="s">
         <v>1844</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
-      <c r="B181" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" t="s">
+    <row r="189" spans="1:5">
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
         <v>3611</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B191" t="s">
         <v>3612</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E191" t="s">
         <v>3613</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
-      <c r="A186" t="s">
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
         <v>1850</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B194" t="s">
         <v>1854</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E194" t="s">
         <v>1851</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
-      <c r="B187" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" t="s">
+    <row r="195" spans="1:5">
+      <c r="B195" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
         <v>1852</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B197" t="s">
         <v>1855</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E197" t="s">
         <v>1853</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
-      <c r="B190" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" t="s">
+    <row r="198" spans="1:5">
+      <c r="B198" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
         <v>1846</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B200" t="s">
         <v>1856</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E200" t="s">
         <v>1848</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
-      <c r="B193" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8">
-      <c r="A195" t="s">
+    <row r="201" spans="1:5">
+      <c r="B201" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
         <v>1847</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B203" t="s">
         <v>1857</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E203" t="s">
         <v>1849</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
-      <c r="B196" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8">
-      <c r="A198" t="s">
+    <row r="204" spans="1:5">
+      <c r="B204" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
         <v>3053</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B206" t="s">
         <v>3055</v>
       </c>
-      <c r="E198">
+      <c r="E206">
         <v>617676</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
-      <c r="A199" t="s">
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
         <v>3054</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B207" t="s">
         <v>3056</v>
       </c>
-      <c r="E199">
+      <c r="E207">
         <v>89117</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
-      <c r="A200" t="s">
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
         <v>3109</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B208" t="s">
         <v>3112</v>
       </c>
-      <c r="E200">
+      <c r="E208">
         <v>9215400007</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8">
-      <c r="A201" t="s">
-        <v>3110</v>
-      </c>
-      <c r="B201" t="s">
-        <v>3111</v>
-      </c>
-      <c r="E201">
-        <v>9215400006</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="A202" t="s">
-        <v>3058</v>
-      </c>
-      <c r="B202" t="s">
-        <v>3059</v>
-      </c>
-      <c r="E202" t="s">
-        <v>3057</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8">
-      <c r="A204" t="s">
-        <v>3230</v>
-      </c>
-      <c r="B204" t="s">
-        <v>3231</v>
-      </c>
-      <c r="E204" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8">
-      <c r="A206" t="s">
-        <v>3626</v>
-      </c>
-      <c r="B206" t="s">
-        <v>3627</v>
-      </c>
-      <c r="D206" t="s">
-        <v>3628</v>
-      </c>
-      <c r="H206" t="str">
-        <f>"::"&amp;A206&amp;"::"&amp;B206</f>
-        <v>::xx120::1SFA611130R1108</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
-      <c r="A207" t="s">
-        <v>3629</v>
-      </c>
-      <c r="B207" t="s">
-        <v>3632</v>
-      </c>
-      <c r="D207" t="s">
-        <v>3633</v>
-      </c>
-      <c r="H207" t="str">
-        <f>"::"&amp;A207&amp;"::"&amp;B207</f>
-        <v>::xx121::1SFA611605R1100</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8">
-      <c r="A208" t="s">
-        <v>3630</v>
-      </c>
-      <c r="B208" t="s">
-        <v>3634</v>
-      </c>
-      <c r="D208" t="s">
-        <v>3638</v>
-      </c>
-      <c r="H208" t="str">
-        <f t="shared" ref="H208:H210" si="0">"::"&amp;A208&amp;"::"&amp;B208</f>
-        <v>::xx122::1SFA611610R1001</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>3631</v>
+        <v>3110</v>
       </c>
       <c r="B209" t="s">
-        <v>3635</v>
-      </c>
-      <c r="D209" t="s">
-        <v>3639</v>
-      </c>
-      <c r="H209" t="str">
-        <f t="shared" si="0"/>
-        <v>::xx123::1SFA611610R1010</v>
+        <v>3111</v>
+      </c>
+      <c r="E209">
+        <v>9215400006</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B210" t="s">
+        <v>3059</v>
+      </c>
+      <c r="E210" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B212" t="s">
+        <v>3231</v>
+      </c>
+      <c r="E212" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>3626</v>
+      </c>
+      <c r="B214" t="s">
+        <v>3627</v>
+      </c>
+      <c r="D214" t="s">
+        <v>3628</v>
+      </c>
+      <c r="H214" t="str">
+        <f>"::"&amp;A214&amp;"::"&amp;B214</f>
+        <v>::xx120::1SFA611130R1108</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>3629</v>
+      </c>
+      <c r="B215" t="s">
+        <v>3632</v>
+      </c>
+      <c r="D215" t="s">
+        <v>3633</v>
+      </c>
+      <c r="H215" t="str">
+        <f>"::"&amp;A215&amp;"::"&amp;B215</f>
+        <v>::xx121::1SFA611605R1100</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" t="s">
+        <v>3630</v>
+      </c>
+      <c r="B216" t="s">
+        <v>3634</v>
+      </c>
+      <c r="D216" t="s">
+        <v>3638</v>
+      </c>
+      <c r="H216" t="str">
+        <f t="shared" ref="H216:H218" si="0">"::"&amp;A216&amp;"::"&amp;B216</f>
+        <v>::xx122::1SFA611610R1001</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B217" t="s">
+        <v>3635</v>
+      </c>
+      <c r="D217" t="s">
+        <v>3639</v>
+      </c>
+      <c r="H217" t="str">
+        <f t="shared" si="0"/>
+        <v>::xx123::1SFA611610R1010</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
         <v>3636</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B218" t="s">
         <v>3637</v>
       </c>
-      <c r="D210" t="s">
+      <c r="D218" t="s">
         <v>3640</v>
       </c>
-      <c r="H210" t="str">
+      <c r="H218" t="str">
         <f t="shared" si="0"/>
         <v>::xx124::1SFA611621R1075</v>
       </c>
